--- a/Data/MovesPokemon.xlsx
+++ b/Data/MovesPokemon.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19470" windowHeight="12060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19470" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1568,15 +1568,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1584,353 +1580,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1938,313 +1597,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
-    <cellStyle name="Observação" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Saída" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
-    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Bom" xfId="22" builtinId="26"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
-    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
-    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
-    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
-    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
-    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
+      <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -2265,16 +1648,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:J225" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J225" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="MIRROR MOVE"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:J225">
+    <filterColumn colId="1"/>
   </autoFilter>
-  <sortState ref="A1:J225">
-    <sortCondition ref="A1"/>
-  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="NAME"/>
@@ -2543,24 +1919,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J225"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.28571428571429" customWidth="1"/>
-    <col min="2" max="2" width="17.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="5" max="5" width="5.14285714285714" customWidth="1"/>
-    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5.57142857142857" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="14.2857142857143" customWidth="1"/>
-    <col min="10" max="10" width="14.5714285714286" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2595,7 +1971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2612,7 +1988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2629,7 +2005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2652,7 +2028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2672,7 +2048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2695,7 +2071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2715,7 +2091,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2738,7 +2114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2758,7 +2134,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2781,7 +2157,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2801,7 +2177,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2824,7 +2200,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:8">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2841,7 +2217,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2861,7 +2237,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2878,7 +2254,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:8">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2898,7 +2274,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:8">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2921,7 +2297,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:8">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2944,7 +2320,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:8">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2961,7 +2337,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:8">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2978,7 +2354,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:8">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3001,7 +2377,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:8">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3021,7 +2397,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:8">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3041,7 +2417,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:8">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3067,7 +2443,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:8">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3087,7 +2463,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:8">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3104,7 +2480,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:8">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3124,7 +2500,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:8">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3144,7 +2520,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:8">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3167,7 +2543,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:8">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3187,7 +2563,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:8">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3210,7 +2586,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:8">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3233,7 +2609,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:8">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3256,7 +2632,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:8">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3276,7 +2652,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:8">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3296,7 +2672,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:8">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3336,7 +2712,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:8">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3353,7 +2729,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:8">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3370,7 +2746,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:8">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3390,7 +2766,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:8">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3413,7 +2789,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:8">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3436,7 +2812,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:8">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3462,7 +2838,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:8">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3479,7 +2855,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:8">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3496,7 +2872,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:8">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3519,7 +2895,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:8">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3542,7 +2918,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:8">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3562,7 +2938,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:8">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3579,7 +2955,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:8">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3602,7 +2978,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:8">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3625,7 +3001,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:8">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3648,7 +3024,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:8">
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3665,7 +3041,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:8">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3691,7 +3067,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:8">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3711,7 +3087,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:8">
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3737,7 +3113,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:8">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3757,7 +3133,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:8">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3780,7 +3156,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:8">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3803,7 +3179,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:8">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3826,7 +3202,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:8">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3849,7 +3225,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:8">
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3869,7 +3245,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:8">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3886,7 +3262,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:8">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3909,7 +3285,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:8">
+    <row r="65" spans="1:10">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3932,7 +3308,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:8">
+    <row r="66" spans="1:10">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3955,7 +3331,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:8">
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3975,7 +3351,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:8">
+    <row r="68" spans="1:10">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3998,7 +3374,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:8">
+    <row r="69" spans="1:10">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4021,7 +3397,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:8">
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4041,7 +3417,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:10">
+    <row r="71" spans="1:10">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -4063,7 +3439,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" hidden="1" spans="1:8">
+    <row r="72" spans="1:10">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4086,7 +3462,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:8">
+    <row r="73" spans="1:10">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4112,7 +3488,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:8">
+    <row r="74" spans="1:10">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4132,7 +3508,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:8">
+    <row r="75" spans="1:10">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4149,7 +3525,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:8">
+    <row r="76" spans="1:10">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4172,7 +3548,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:8">
+    <row r="77" spans="1:10">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4195,7 +3571,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:8">
+    <row r="78" spans="1:10">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4215,7 +3591,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:10">
+    <row r="79" spans="1:10">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -4239,7 +3615,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
     </row>
-    <row r="80" hidden="1" spans="1:10">
+    <row r="80" spans="1:10">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -4265,7 +3641,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
     </row>
-    <row r="81" hidden="1" spans="1:10">
+    <row r="81" spans="1:10">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -4289,7 +3665,7 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" hidden="1" spans="1:8">
+    <row r="82" spans="1:10">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4306,7 +3682,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:8">
+    <row r="83" spans="1:10">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -4323,7 +3699,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:8">
+    <row r="84" spans="1:10">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -4346,7 +3722,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:8">
+    <row r="85" spans="1:10">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -4366,7 +3742,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:8">
+    <row r="86" spans="1:10">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -4386,7 +3762,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:8">
+    <row r="87" spans="1:10">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -4403,7 +3779,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:10">
+    <row r="88" spans="1:10">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -4429,7 +3805,7 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" hidden="1" spans="1:10">
+    <row r="89" spans="1:10">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4453,7 +3829,7 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" hidden="1" spans="1:10">
+    <row r="90" spans="1:10">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -4477,7 +3853,7 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" hidden="1" spans="1:10">
+    <row r="91" spans="1:10">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -4505,7 +3881,7 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" hidden="1" spans="1:10">
+    <row r="92" spans="1:10">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4529,7 +3905,7 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" hidden="1" spans="1:10">
+    <row r="93" spans="1:10">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4555,7 +3931,7 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
     </row>
-    <row r="94" hidden="1" spans="1:8">
+    <row r="94" spans="1:10">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4575,7 +3951,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:8">
+    <row r="95" spans="1:10">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4595,7 +3971,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:10">
+    <row r="96" spans="1:10">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4621,7 +3997,7 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
     </row>
-    <row r="97" hidden="1" spans="1:10">
+    <row r="97" spans="1:10">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4647,7 +4023,7 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
     </row>
-    <row r="98" hidden="1" spans="1:8">
+    <row r="98" spans="1:10">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4667,7 +4043,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:8">
+    <row r="99" spans="1:10">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -4690,7 +4066,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:8">
+    <row r="100" spans="1:10">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -4713,7 +4089,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:8">
+    <row r="101" spans="1:10">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4736,7 +4112,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:8">
+    <row r="102" spans="1:10">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4759,7 +4135,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:8">
+    <row r="103" spans="1:10">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4782,7 +4158,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:8">
+    <row r="104" spans="1:10">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4802,7 +4178,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:8">
+    <row r="105" spans="1:10">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4825,7 +4201,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:8">
+    <row r="106" spans="1:10">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4851,7 +4227,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:8">
+    <row r="107" spans="1:10">
       <c r="A107">
         <v>106</v>
       </c>
@@ -4874,7 +4250,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:8">
+    <row r="108" spans="1:10">
       <c r="A108">
         <v>107</v>
       </c>
@@ -4894,7 +4270,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:8">
+    <row r="109" spans="1:10">
       <c r="A109">
         <v>108</v>
       </c>
@@ -4917,7 +4293,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:8">
+    <row r="110" spans="1:10">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4940,7 +4316,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:8">
+    <row r="111" spans="1:10">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4963,7 +4339,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:8">
+    <row r="112" spans="1:10">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4986,7 +4362,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:8">
+    <row r="113" spans="1:8">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5009,7 +4385,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:8">
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5026,7 +4402,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:8">
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5046,7 +4422,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:8">
+    <row r="116" spans="1:8">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5069,7 +4445,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:8">
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5089,7 +4465,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:8">
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5109,7 +4485,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:8">
+    <row r="119" spans="1:8">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5135,7 +4511,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:8">
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5158,7 +4534,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:8">
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5181,7 +4557,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:8">
+    <row r="122" spans="1:8">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5201,7 +4577,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:8">
+    <row r="123" spans="1:8">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5218,7 +4594,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:8">
+    <row r="124" spans="1:8">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5235,7 +4611,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:8">
+    <row r="125" spans="1:8">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5255,7 +4631,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:8">
+    <row r="126" spans="1:8">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5278,7 +4654,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:8">
+    <row r="127" spans="1:8">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5301,7 +4677,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:8">
+    <row r="128" spans="1:8">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5324,7 +4700,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:8">
+    <row r="129" spans="1:8">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5344,7 +4720,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:8">
+    <row r="130" spans="1:8">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5364,7 +4740,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:8">
+    <row r="131" spans="1:8">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5387,7 +4763,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:8">
+    <row r="132" spans="1:8">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5410,7 +4786,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:8">
+    <row r="133" spans="1:8">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5427,7 +4803,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:8">
+    <row r="134" spans="1:8">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5450,7 +4826,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:8">
+    <row r="135" spans="1:8">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5467,7 +4843,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:8">
+    <row r="136" spans="1:8">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5490,7 +4866,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:8">
+    <row r="137" spans="1:8">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5510,7 +4886,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:8">
+    <row r="138" spans="1:8">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5530,7 +4906,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:8">
+    <row r="139" spans="1:8">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5553,7 +4929,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:8">
+    <row r="140" spans="1:8">
       <c r="A140">
         <v>139</v>
       </c>
@@ -5573,7 +4949,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:8">
+    <row r="141" spans="1:8">
       <c r="A141">
         <v>140</v>
       </c>
@@ -5596,7 +4972,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:8">
+    <row r="142" spans="1:8">
       <c r="A142">
         <v>141</v>
       </c>
@@ -5616,7 +4992,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:8">
+    <row r="143" spans="1:8">
       <c r="A143">
         <v>142</v>
       </c>
@@ -5639,7 +5015,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:8">
+    <row r="144" spans="1:8">
       <c r="A144">
         <v>143</v>
       </c>
@@ -5656,7 +5032,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:8">
+    <row r="145" spans="1:8">
       <c r="A145">
         <v>144</v>
       </c>
@@ -5679,7 +5055,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:8">
+    <row r="146" spans="1:8">
       <c r="A146">
         <v>145</v>
       </c>
@@ -5699,7 +5075,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:8">
+    <row r="147" spans="1:8">
       <c r="A147">
         <v>146</v>
       </c>
@@ -5722,7 +5098,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:8">
+    <row r="148" spans="1:8">
       <c r="A148">
         <v>147</v>
       </c>
@@ -5742,7 +5118,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:8">
+    <row r="149" spans="1:8">
       <c r="A149">
         <v>148</v>
       </c>
@@ -5759,7 +5135,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:8">
+    <row r="150" spans="1:8">
       <c r="A150">
         <v>149</v>
       </c>
@@ -5779,7 +5155,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:8">
+    <row r="151" spans="1:8">
       <c r="A151">
         <v>150</v>
       </c>
@@ -5802,7 +5178,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:8">
+    <row r="152" spans="1:8">
       <c r="A152">
         <v>151</v>
       </c>
@@ -5822,7 +5198,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:8">
+    <row r="153" spans="1:8">
       <c r="A153">
         <v>152</v>
       </c>
@@ -5845,7 +5221,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:8">
+    <row r="154" spans="1:8">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5865,7 +5241,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="155" hidden="1" spans="1:8">
+    <row r="155" spans="1:8">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5888,7 +5264,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:8">
+    <row r="156" spans="1:8">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5914,7 +5290,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:8">
+    <row r="157" spans="1:8">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5937,7 +5313,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:8">
+    <row r="158" spans="1:8">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5960,7 +5336,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:8">
+    <row r="159" spans="1:8">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5977,7 +5353,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="1:8">
+    <row r="160" spans="1:8">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5994,7 +5370,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:8">
+    <row r="161" spans="1:8">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6011,7 +5387,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:8">
+    <row r="162" spans="1:8">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6034,7 +5410,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:8">
+    <row r="163" spans="1:8">
       <c r="A163">
         <v>162</v>
       </c>
@@ -6051,7 +5427,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:8">
+    <row r="164" spans="1:8">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6071,7 +5447,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="165" hidden="1" spans="1:8">
+    <row r="165" spans="1:8">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6088,7 +5464,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:8">
+    <row r="166" spans="1:8">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6108,7 +5484,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:8">
+    <row r="167" spans="1:8">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6128,7 +5504,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:8">
+    <row r="168" spans="1:8">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6148,7 +5524,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:8">
+    <row r="169" spans="1:8">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6168,7 +5544,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:8">
+    <row r="170" spans="1:8">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6188,7 +5564,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:8">
+    <row r="171" spans="1:8">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6211,7 +5587,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:8">
+    <row r="172" spans="1:8">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6231,7 +5607,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:8">
+    <row r="173" spans="1:8">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6254,7 +5630,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:8">
+    <row r="174" spans="1:8">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6274,7 +5650,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:8">
+    <row r="175" spans="1:8">
       <c r="A175">
         <v>175</v>
       </c>
@@ -6294,7 +5670,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:8">
+    <row r="176" spans="1:8">
       <c r="A176">
         <v>176</v>
       </c>
@@ -6314,7 +5690,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:8">
+    <row r="177" spans="1:8">
       <c r="A177">
         <v>177</v>
       </c>
@@ -6334,7 +5710,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:8">
+    <row r="178" spans="1:8">
       <c r="A178">
         <v>179</v>
       </c>
@@ -6354,7 +5730,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:8">
+    <row r="179" spans="1:8">
       <c r="A179">
         <v>180</v>
       </c>
@@ -6374,7 +5750,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:8">
+    <row r="180" spans="1:8">
       <c r="A180">
         <v>181</v>
       </c>
@@ -6397,7 +5773,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:8">
+    <row r="181" spans="1:8">
       <c r="A181">
         <v>182</v>
       </c>
@@ -6420,7 +5796,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="182" hidden="1" customHeight="1" spans="1:8">
+    <row r="182" spans="1:8" ht="15" customHeight="1">
       <c r="A182">
         <v>183</v>
       </c>
@@ -6440,7 +5816,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="1:8">
+    <row r="183" spans="1:8">
       <c r="A183">
         <v>184</v>
       </c>
@@ -6460,7 +5836,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="1:8">
+    <row r="184" spans="1:8">
       <c r="A184">
         <v>185</v>
       </c>
@@ -6483,7 +5859,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="185" hidden="1" spans="1:8">
+    <row r="185" spans="1:8">
       <c r="A185">
         <v>186</v>
       </c>
@@ -6503,7 +5879,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:8">
+    <row r="186" spans="1:8">
       <c r="A186">
         <v>187</v>
       </c>
@@ -6523,7 +5899,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:8">
+    <row r="187" spans="1:8">
       <c r="A187">
         <v>188</v>
       </c>
@@ -6546,7 +5922,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:8">
+    <row r="188" spans="1:8">
       <c r="A188">
         <v>189</v>
       </c>
@@ -6566,7 +5942,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:8">
+    <row r="189" spans="1:8">
       <c r="A189">
         <v>190</v>
       </c>
@@ -6586,7 +5962,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="190" hidden="1" spans="1:8">
+    <row r="190" spans="1:8">
       <c r="A190">
         <v>191</v>
       </c>
@@ -6603,7 +5979,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="191" hidden="1" spans="1:8">
+    <row r="191" spans="1:8">
       <c r="A191">
         <v>192</v>
       </c>
@@ -6623,7 +5999,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="192" hidden="1" spans="1:8">
+    <row r="192" spans="1:8">
       <c r="A192">
         <v>193</v>
       </c>
@@ -6643,7 +6019,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="193" hidden="1" spans="1:8">
+    <row r="193" spans="1:8">
       <c r="A193">
         <v>194</v>
       </c>
@@ -6666,7 +6042,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="194" hidden="1" spans="1:8">
+    <row r="194" spans="1:8">
       <c r="A194">
         <v>195</v>
       </c>
@@ -6689,7 +6065,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="195" hidden="1" spans="1:8">
+    <row r="195" spans="1:8">
       <c r="A195">
         <v>196</v>
       </c>
@@ -6709,7 +6085,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="196" hidden="1" spans="1:8">
+    <row r="196" spans="1:8">
       <c r="A196">
         <v>197</v>
       </c>
@@ -6732,7 +6108,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="197" hidden="1" spans="1:8">
+    <row r="197" spans="1:8">
       <c r="A197">
         <v>198</v>
       </c>
@@ -6752,7 +6128,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="198" hidden="1" spans="1:8">
+    <row r="198" spans="1:8">
       <c r="A198">
         <v>199</v>
       </c>
@@ -6772,7 +6148,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="199" hidden="1" spans="1:8">
+    <row r="199" spans="1:8">
       <c r="A199">
         <v>200</v>
       </c>
@@ -6792,7 +6168,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="200" hidden="1" spans="1:8">
+    <row r="200" spans="1:8">
       <c r="A200">
         <v>201</v>
       </c>
@@ -6815,7 +6191,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="201" hidden="1" spans="1:8">
+    <row r="201" spans="1:8">
       <c r="A201">
         <v>202</v>
       </c>
@@ -6835,7 +6211,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="202" hidden="1" spans="1:8">
+    <row r="202" spans="1:8">
       <c r="A202">
         <v>203</v>
       </c>
@@ -6855,7 +6231,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="203" hidden="1" spans="1:8">
+    <row r="203" spans="1:8">
       <c r="A203">
         <v>204</v>
       </c>
@@ -6875,7 +6251,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="204" hidden="1" spans="1:8">
+    <row r="204" spans="1:8">
       <c r="A204">
         <v>205</v>
       </c>
@@ -6895,7 +6271,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="205" hidden="1" spans="1:8">
+    <row r="205" spans="1:8">
       <c r="A205">
         <v>206</v>
       </c>
@@ -6915,7 +6291,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="206" hidden="1" spans="1:8">
+    <row r="206" spans="1:8">
       <c r="A206">
         <v>207</v>
       </c>
@@ -6935,7 +6311,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="207" hidden="1" spans="1:8">
+    <row r="207" spans="1:8">
       <c r="A207">
         <v>208</v>
       </c>
@@ -6955,7 +6331,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="208" hidden="1" spans="1:8">
+    <row r="208" spans="1:8">
       <c r="A208">
         <v>209</v>
       </c>
@@ -6975,7 +6351,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="209" hidden="1" spans="1:8">
+    <row r="209" spans="1:8">
       <c r="A209">
         <v>210</v>
       </c>
@@ -6995,7 +6371,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="210" hidden="1" spans="1:8">
+    <row r="210" spans="1:8">
       <c r="A210">
         <v>211</v>
       </c>
@@ -7018,7 +6394,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="211" hidden="1" spans="1:8">
+    <row r="211" spans="1:8">
       <c r="A211">
         <v>212</v>
       </c>
@@ -7038,7 +6414,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="212" hidden="1" spans="1:8">
+    <row r="212" spans="1:8">
       <c r="A212">
         <v>213</v>
       </c>
@@ -7058,7 +6434,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="213" hidden="1" spans="1:8">
+    <row r="213" spans="1:8">
       <c r="A213">
         <v>214</v>
       </c>
@@ -7084,7 +6460,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="214" hidden="1" spans="1:8">
+    <row r="214" spans="1:8">
       <c r="A214">
         <v>215</v>
       </c>
@@ -7107,7 +6483,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="215" hidden="1" spans="1:8">
+    <row r="215" spans="1:8">
       <c r="A215">
         <v>216</v>
       </c>
@@ -7127,7 +6503,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="216" hidden="1" spans="1:8">
+    <row r="216" spans="1:8">
       <c r="A216">
         <v>217</v>
       </c>
@@ -7147,7 +6523,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="217" hidden="1" spans="1:8">
+    <row r="217" spans="1:8">
       <c r="A217">
         <v>218</v>
       </c>
@@ -7167,7 +6543,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="218" hidden="1" spans="1:8">
+    <row r="218" spans="1:8">
       <c r="A218">
         <v>219</v>
       </c>
@@ -7187,7 +6563,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="219" hidden="1" spans="1:8">
+    <row r="219" spans="1:8">
       <c r="A219">
         <v>220</v>
       </c>
@@ -7210,7 +6586,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="220" hidden="1" spans="1:8">
+    <row r="220" spans="1:8">
       <c r="A220">
         <v>221</v>
       </c>
@@ -7233,7 +6609,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="221" hidden="1" spans="1:8">
+    <row r="221" spans="1:8">
       <c r="A221">
         <v>222</v>
       </c>
@@ -7253,7 +6629,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="222" hidden="1" spans="1:8">
+    <row r="222" spans="1:8">
       <c r="A222">
         <v>223</v>
       </c>
@@ -7273,7 +6649,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="223" hidden="1" spans="1:8">
+    <row r="223" spans="1:8">
       <c r="A223">
         <v>224</v>
       </c>
@@ -7290,7 +6666,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="224" hidden="1" spans="1:8">
+    <row r="224" spans="1:8">
       <c r="A224">
         <v>225</v>
       </c>
@@ -7313,7 +6689,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="225" hidden="1" spans="1:8">
+    <row r="225" spans="1:8">
       <c r="A225">
         <v>226</v>
       </c>
@@ -7332,17 +6708,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A225">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B225">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H$1:H$1048576">
+  <conditionalFormatting sqref="H1:H1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
